--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120975335</v>
+        <v>120975339</v>
       </c>
       <c r="B2" t="n">
-        <v>78334</v>
+        <v>92008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577449</v>
+        <v>577494</v>
       </c>
       <c r="R2" t="n">
-        <v>6517392</v>
+        <v>6517176</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120975345</v>
+        <v>120973985</v>
       </c>
       <c r="B3" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +827,25 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577514</v>
+        <v>577266</v>
       </c>
       <c r="R3" t="n">
-        <v>6517155</v>
+        <v>6517346</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>8 kuddar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120973982</v>
+        <v>120973976</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,28 +935,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -953,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577367</v>
+        <v>577465</v>
       </c>
       <c r="R4" t="n">
-        <v>6517396</v>
+        <v>6517394</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -988,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120973991</v>
+        <v>120973978</v>
       </c>
       <c r="B5" t="n">
-        <v>94844</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,31 +1046,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1069,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577465</v>
+        <v>577252</v>
       </c>
       <c r="R5" t="n">
-        <v>6517394</v>
+        <v>6517300</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1156,7 @@
         <v>120975341</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1260,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120973981</v>
+        <v>120973983</v>
       </c>
       <c r="B7" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1293,7 +1305,11 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1303,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577341</v>
+        <v>577417</v>
       </c>
       <c r="R7" t="n">
-        <v>6517367</v>
+        <v>6517412</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1338,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120973980</v>
+        <v>120973982</v>
       </c>
       <c r="B8" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,7 +1426,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1422,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577235</v>
+        <v>577367</v>
       </c>
       <c r="R8" t="n">
-        <v>6517371</v>
+        <v>6517396</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1457,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1483,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120973990</v>
+        <v>120975338</v>
       </c>
       <c r="B9" t="n">
-        <v>94844</v>
+        <v>92008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,42 +1522,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577413</v>
+        <v>577432</v>
       </c>
       <c r="R9" t="n">
-        <v>6517390</v>
+        <v>6517199</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1573,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1602,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120973985</v>
+        <v>120973984</v>
       </c>
       <c r="B10" t="n">
-        <v>94844</v>
+        <v>92008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,35 +1641,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1658,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577266</v>
+        <v>577445</v>
       </c>
       <c r="R10" t="n">
-        <v>6517346</v>
+        <v>6517399</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1693,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,12 +1721,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>8 kuddar</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120975347</v>
+        <v>120973979</v>
       </c>
       <c r="B11" t="n">
-        <v>94844</v>
+        <v>92008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,42 +1760,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577569</v>
+        <v>577264</v>
       </c>
       <c r="R11" t="n">
-        <v>6517097</v>
+        <v>6517355</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1814,7 +1830,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1824,7 +1840,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120975342</v>
+        <v>120975346</v>
       </c>
       <c r="B12" t="n">
-        <v>91998</v>
+        <v>94854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,34 +1879,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1933,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,7 +1956,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120973987</v>
+        <v>120975335</v>
       </c>
       <c r="B13" t="n">
-        <v>94844</v>
+        <v>78337</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,42 +1995,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577264</v>
+        <v>577449</v>
       </c>
       <c r="R13" t="n">
-        <v>6517369</v>
+        <v>6517392</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2049,7 +2061,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +2071,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2098,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120973978</v>
+        <v>120973990</v>
       </c>
       <c r="B14" t="n">
-        <v>91998</v>
+        <v>94854</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,34 +2110,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2133,13 +2142,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577252</v>
+        <v>577413</v>
       </c>
       <c r="R14" t="n">
-        <v>6517300</v>
+        <v>6517390</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2168,7 +2177,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,7 +2187,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,10 +2214,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120973984</v>
+        <v>120975342</v>
       </c>
       <c r="B15" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2240,7 +2249,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2248,14 +2257,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577445</v>
+        <v>577569</v>
       </c>
       <c r="R15" t="n">
-        <v>6517399</v>
+        <v>6517097</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2287,7 +2296,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2306,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,10 +2333,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120973983</v>
+        <v>120973991</v>
       </c>
       <c r="B16" t="n">
-        <v>91998</v>
+        <v>94854</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2336,34 +2345,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2371,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577417</v>
+        <v>577465</v>
       </c>
       <c r="R16" t="n">
-        <v>6517412</v>
+        <v>6517394</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2406,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2416,7 +2422,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120973989</v>
+        <v>120973980</v>
       </c>
       <c r="B17" t="n">
-        <v>94844</v>
+        <v>92008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2455,31 +2461,34 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2487,10 +2496,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577337</v>
+        <v>577235</v>
       </c>
       <c r="R17" t="n">
-        <v>6517372</v>
+        <v>6517371</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2522,7 +2531,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2532,7 +2541,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2559,10 +2568,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120975338</v>
+        <v>120975345</v>
       </c>
       <c r="B18" t="n">
-        <v>91998</v>
+        <v>94854</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2571,34 +2580,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2606,10 +2612,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577432</v>
+        <v>577514</v>
       </c>
       <c r="R18" t="n">
-        <v>6517199</v>
+        <v>6517155</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2641,7 +2647,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2651,7 +2657,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,10 +2684,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120973976</v>
+        <v>120973987</v>
       </c>
       <c r="B19" t="n">
-        <v>78334</v>
+        <v>94854</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2690,30 +2696,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2721,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577465</v>
+        <v>577264</v>
       </c>
       <c r="R19" t="n">
-        <v>6517394</v>
+        <v>6517369</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2756,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2793,10 +2800,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120973979</v>
+        <v>120973981</v>
       </c>
       <c r="B20" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2826,11 +2833,7 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2840,10 +2843,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577264</v>
+        <v>577341</v>
       </c>
       <c r="R20" t="n">
-        <v>6517355</v>
+        <v>6517367</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2875,7 +2878,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2885,7 +2888,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2912,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120975339</v>
+        <v>120973989</v>
       </c>
       <c r="B21" t="n">
-        <v>91998</v>
+        <v>94854</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2924,45 +2927,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577494</v>
+        <v>577337</v>
       </c>
       <c r="R21" t="n">
-        <v>6517176</v>
+        <v>6517372</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3034,7 +3034,7 @@
         <v>121174193</v>
       </c>
       <c r="B22" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120975339</v>
+        <v>120973985</v>
       </c>
       <c r="B2" t="n">
-        <v>92008</v>
+        <v>94854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577494</v>
+        <v>577266</v>
       </c>
       <c r="R2" t="n">
-        <v>6517176</v>
+        <v>6517346</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>8 kuddar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120973985</v>
+        <v>120975339</v>
       </c>
       <c r="B3" t="n">
-        <v>94854</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,46 +812,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577266</v>
+        <v>577494</v>
       </c>
       <c r="R3" t="n">
-        <v>6517346</v>
+        <v>6517176</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>8 kuddar</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120973985</v>
+        <v>120975339</v>
       </c>
       <c r="B2" t="n">
-        <v>94854</v>
+        <v>92008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577266</v>
+        <v>577494</v>
       </c>
       <c r="R2" t="n">
-        <v>6517346</v>
+        <v>6517176</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>8 kuddar</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120975339</v>
+        <v>120973985</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,45 +806,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577494</v>
+        <v>577266</v>
       </c>
       <c r="R3" t="n">
-        <v>6517176</v>
+        <v>6517346</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -882,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>8 kuddar</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120975339</v>
+        <v>120973991</v>
       </c>
       <c r="B2" t="n">
-        <v>92008</v>
+        <v>94854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,45 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577494</v>
+        <v>577465</v>
       </c>
       <c r="R2" t="n">
-        <v>6517176</v>
+        <v>6517394</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120973985</v>
+        <v>120973983</v>
       </c>
       <c r="B3" t="n">
-        <v>94854</v>
+        <v>92008</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +803,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577266</v>
+        <v>577417</v>
       </c>
       <c r="R3" t="n">
-        <v>6517346</v>
+        <v>6517412</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>8 kuddar</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120973976</v>
+        <v>120973980</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>92008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,24 +926,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -962,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577465</v>
+        <v>577235</v>
       </c>
       <c r="R4" t="n">
-        <v>6517394</v>
+        <v>6517371</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -997,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120973978</v>
+        <v>120975340</v>
       </c>
       <c r="B5" t="n">
         <v>92008</v>
@@ -1077,17 +1072,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577252</v>
+        <v>577514</v>
       </c>
       <c r="R5" t="n">
-        <v>6517300</v>
+        <v>6517155</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120975341</v>
+        <v>120973976</v>
       </c>
       <c r="B6" t="n">
-        <v>92008</v>
+        <v>78337</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,41 +1164,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577514</v>
+        <v>577465</v>
       </c>
       <c r="R6" t="n">
-        <v>6517155</v>
+        <v>6517394</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1235,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120973983</v>
+        <v>120973985</v>
       </c>
       <c r="B7" t="n">
-        <v>92008</v>
+        <v>94854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,34 +1275,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577417</v>
+        <v>577266</v>
       </c>
       <c r="R7" t="n">
-        <v>6517412</v>
+        <v>6517346</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1354,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1356,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>8 kuddar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,7 +1388,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120973982</v>
+        <v>120973978</v>
       </c>
       <c r="B8" t="n">
         <v>92008</v>
@@ -1426,7 +1423,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1438,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577367</v>
+        <v>577252</v>
       </c>
       <c r="R8" t="n">
-        <v>6517396</v>
+        <v>6517300</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1473,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1483,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120975338</v>
+        <v>120975335</v>
       </c>
       <c r="B9" t="n">
-        <v>92008</v>
+        <v>78337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,28 +1523,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1557,10 +1550,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577432</v>
+        <v>577449</v>
       </c>
       <c r="R9" t="n">
-        <v>6517199</v>
+        <v>6517392</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1592,7 +1585,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1595,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,17 +1615,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120973984</v>
+        <v>120975345</v>
       </c>
       <c r="B10" t="n">
-        <v>92008</v>
+        <v>94854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,45 +1634,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577445</v>
+        <v>577514</v>
       </c>
       <c r="R10" t="n">
-        <v>6517399</v>
+        <v>6517155</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1711,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,7 +1738,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120973979</v>
+        <v>120975342</v>
       </c>
       <c r="B11" t="n">
         <v>92008</v>
@@ -1783,7 +1773,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1791,14 +1781,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577264</v>
+        <v>577569</v>
       </c>
       <c r="R11" t="n">
-        <v>6517355</v>
+        <v>6517097</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1830,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120975346</v>
+        <v>120973979</v>
       </c>
       <c r="B12" t="n">
-        <v>94854</v>
+        <v>92008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,42 +1869,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577569</v>
+        <v>577264</v>
       </c>
       <c r="R12" t="n">
-        <v>6517097</v>
+        <v>6517355</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1946,7 +1939,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,7 +1949,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120975335</v>
+        <v>120975339</v>
       </c>
       <c r="B13" t="n">
-        <v>78337</v>
+        <v>92008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,24 +1992,28 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -2026,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577449</v>
+        <v>577494</v>
       </c>
       <c r="R13" t="n">
-        <v>6517392</v>
+        <v>6517176</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2061,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2071,7 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,7 +2211,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120975342</v>
+        <v>120975338</v>
       </c>
       <c r="B15" t="n">
         <v>92008</v>
@@ -2249,7 +2246,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -2261,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577569</v>
+        <v>577432</v>
       </c>
       <c r="R15" t="n">
-        <v>6517097</v>
+        <v>6517199</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2296,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2306,7 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,7 +2330,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120973991</v>
+        <v>120973989</v>
       </c>
       <c r="B16" t="n">
         <v>94854</v>
@@ -2377,10 +2374,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577465</v>
+        <v>577337</v>
       </c>
       <c r="R16" t="n">
-        <v>6517394</v>
+        <v>6517372</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2412,7 +2409,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,7 +2419,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2446,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120973980</v>
+        <v>120975347</v>
       </c>
       <c r="B17" t="n">
-        <v>92008</v>
+        <v>94854</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,45 +2458,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577235</v>
+        <v>577569</v>
       </c>
       <c r="R17" t="n">
-        <v>6517371</v>
+        <v>6517097</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2531,7 +2525,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2541,7 +2535,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2568,10 +2562,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120975345</v>
+        <v>120973984</v>
       </c>
       <c r="B18" t="n">
-        <v>94854</v>
+        <v>92008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,42 +2574,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577514</v>
+        <v>577445</v>
       </c>
       <c r="R18" t="n">
-        <v>6517155</v>
+        <v>6517399</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2647,7 +2644,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,7 +2654,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120973987</v>
+        <v>120973982</v>
       </c>
       <c r="B19" t="n">
-        <v>94854</v>
+        <v>92008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2696,31 +2693,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577264</v>
+        <v>577367</v>
       </c>
       <c r="R19" t="n">
-        <v>6517369</v>
+        <v>6517396</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120973981</v>
+        <v>120973987</v>
       </c>
       <c r="B20" t="n">
-        <v>92008</v>
+        <v>94854</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2812,30 +2812,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2843,10 +2844,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577341</v>
+        <v>577264</v>
       </c>
       <c r="R20" t="n">
-        <v>6517367</v>
+        <v>6517369</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2878,7 +2879,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2888,7 +2889,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2915,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120973989</v>
+        <v>120973981</v>
       </c>
       <c r="B21" t="n">
-        <v>94854</v>
+        <v>92008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2927,31 +2928,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577337</v>
+        <v>577341</v>
       </c>
       <c r="R21" t="n">
-        <v>6517372</v>
+        <v>6517367</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120973991</v>
+        <v>120975342</v>
       </c>
       <c r="B2" t="n">
-        <v>94854</v>
+        <v>92020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577465</v>
+        <v>577569</v>
       </c>
       <c r="R2" t="n">
-        <v>6517394</v>
+        <v>6517097</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120973983</v>
+        <v>120973989</v>
       </c>
       <c r="B3" t="n">
-        <v>92008</v>
+        <v>94866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577417</v>
+        <v>577337</v>
       </c>
       <c r="R3" t="n">
-        <v>6517412</v>
+        <v>6517372</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120973980</v>
+        <v>120975345</v>
       </c>
       <c r="B4" t="n">
-        <v>92008</v>
+        <v>94866</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,45 +922,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577235</v>
+        <v>577514</v>
       </c>
       <c r="R4" t="n">
-        <v>6517371</v>
+        <v>6517155</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -992,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120975340</v>
+        <v>120973984</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,7 +1061,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1072,14 +1069,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577514</v>
+        <v>577445</v>
       </c>
       <c r="R5" t="n">
-        <v>6517155</v>
+        <v>6517399</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1111,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120973976</v>
+        <v>120973980</v>
       </c>
       <c r="B6" t="n">
-        <v>78337</v>
+        <v>92020</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,24 +1161,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1191,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577465</v>
+        <v>577235</v>
       </c>
       <c r="R6" t="n">
-        <v>6517394</v>
+        <v>6517371</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1226,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120973985</v>
+        <v>120973981</v>
       </c>
       <c r="B7" t="n">
-        <v>94854</v>
+        <v>92020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,35 +1276,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1311,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577266</v>
+        <v>577341</v>
       </c>
       <c r="R7" t="n">
-        <v>6517346</v>
+        <v>6517367</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,12 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>8 kuddar</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,10 +1379,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120973978</v>
+        <v>120975347</v>
       </c>
       <c r="B8" t="n">
-        <v>92008</v>
+        <v>94866</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,48 +1391,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577252</v>
+        <v>577569</v>
       </c>
       <c r="R8" t="n">
-        <v>6517300</v>
+        <v>6517097</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1470,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,7 +1498,7 @@
         <v>120975335</v>
       </c>
       <c r="B9" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,17 +1603,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120975345</v>
+        <v>120975340</v>
       </c>
       <c r="B10" t="n">
-        <v>94854</v>
+        <v>92020</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,31 +1622,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1701,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120975342</v>
+        <v>120973979</v>
       </c>
       <c r="B11" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,7 +1764,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1781,14 +1772,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577569</v>
+        <v>577264</v>
       </c>
       <c r="R11" t="n">
-        <v>6517097</v>
+        <v>6517355</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1820,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1821,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1848,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120973979</v>
+        <v>120973982</v>
       </c>
       <c r="B12" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,7 +1883,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1904,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577264</v>
+        <v>577367</v>
       </c>
       <c r="R12" t="n">
-        <v>6517355</v>
+        <v>6517396</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1939,7 +1930,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1949,7 +1940,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120975339</v>
+        <v>120973976</v>
       </c>
       <c r="B13" t="n">
-        <v>92008</v>
+        <v>78340</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,41 +1983,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577494</v>
+        <v>577465</v>
       </c>
       <c r="R13" t="n">
-        <v>6517176</v>
+        <v>6517394</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2058,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2082,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120973990</v>
+        <v>120973978</v>
       </c>
       <c r="B14" t="n">
-        <v>94854</v>
+        <v>92020</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,31 +2094,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2139,13 +2129,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577413</v>
+        <v>577252</v>
       </c>
       <c r="R14" t="n">
-        <v>6517390</v>
+        <v>6517300</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2174,7 +2164,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2174,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2214,7 +2204,7 @@
         <v>120975338</v>
       </c>
       <c r="B15" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2330,10 +2320,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120973989</v>
+        <v>120975339</v>
       </c>
       <c r="B16" t="n">
-        <v>94854</v>
+        <v>92020</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,42 +2332,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
+          <t>Skogsbyås, Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577337</v>
+        <v>577494</v>
       </c>
       <c r="R16" t="n">
-        <v>6517372</v>
+        <v>6517176</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2409,7 +2402,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2419,7 +2412,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,10 +2439,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120975347</v>
+        <v>120973991</v>
       </c>
       <c r="B17" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2486,14 +2479,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skogsbyås, Skogsbyås, Srm</t>
+          <t>Sörmlandsleden, Sörmlandsleden, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577569</v>
+        <v>577465</v>
       </c>
       <c r="R17" t="n">
-        <v>6517097</v>
+        <v>6517394</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2525,7 +2518,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2535,7 +2528,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120973984</v>
+        <v>120973985</v>
       </c>
       <c r="B18" t="n">
-        <v>92008</v>
+        <v>94866</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2574,34 +2567,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2609,10 +2603,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577445</v>
+        <v>577266</v>
       </c>
       <c r="R18" t="n">
-        <v>6517399</v>
+        <v>6517346</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2644,7 +2638,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2654,7 +2648,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>8 kuddar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2681,10 +2680,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120973982</v>
+        <v>120973983</v>
       </c>
       <c r="B19" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,10 +2727,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577367</v>
+        <v>577417</v>
       </c>
       <c r="R19" t="n">
-        <v>6517396</v>
+        <v>6517412</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2763,7 +2762,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2773,7 +2772,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2800,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120973987</v>
+        <v>120973990</v>
       </c>
       <c r="B20" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2844,10 +2843,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577264</v>
+        <v>577413</v>
       </c>
       <c r="R20" t="n">
-        <v>6517369</v>
+        <v>6517390</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2879,7 +2878,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2889,7 +2888,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,10 +2915,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120973981</v>
+        <v>120973987</v>
       </c>
       <c r="B21" t="n">
-        <v>92008</v>
+        <v>94866</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,30 +2927,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577341</v>
+        <v>577264</v>
       </c>
       <c r="R21" t="n">
-        <v>6517367</v>
+        <v>6517369</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3034,7 +3034,7 @@
         <v>121174193</v>
       </c>
       <c r="B22" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3034,7 +3034,7 @@
         <v>121174193</v>
       </c>
       <c r="B22" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3034,7 +3034,7 @@
         <v>121174193</v>
       </c>
       <c r="B22" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3147,6 +3147,622 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121516501</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78252</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>353</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skogsbyås, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>577280</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6517445</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121512078</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79225</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skogsbyås, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>577307</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6517405</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121512671</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90733</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skogsbyås, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>577745</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6517128</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121511809</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79225</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skogsbyås, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>577208</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6517447</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121517750</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80564</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skogsbyås, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>577309</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6517327</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121512473</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79225</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skogsbyås, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>577437</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6517104</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kila</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121516501</v>
+        <v>121517750</v>
       </c>
       <c r="B23" t="n">
-        <v>78252</v>
+        <v>80564</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,34 +3166,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577280</v>
+        <v>577309</v>
       </c>
       <c r="R23" t="n">
-        <v>6517445</v>
+        <v>6517327</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3234,6 +3237,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3354,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121512671</v>
+        <v>121516501</v>
       </c>
       <c r="B25" t="n">
-        <v>90733</v>
+        <v>78252</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,21 +3374,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3394,13 +3398,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577745</v>
+        <v>577280</v>
       </c>
       <c r="R25" t="n">
-        <v>6517128</v>
+        <v>6517445</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3456,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121511809</v>
+        <v>121512671</v>
       </c>
       <c r="B26" t="n">
-        <v>79225</v>
+        <v>90733</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,21 +3476,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3496,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577208</v>
+        <v>577745</v>
       </c>
       <c r="R26" t="n">
-        <v>6517447</v>
+        <v>6517128</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3558,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121517750</v>
+        <v>121511679</v>
       </c>
       <c r="B27" t="n">
-        <v>80564</v>
+        <v>79225</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3574,40 +3578,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577309</v>
+        <v>577208</v>
       </c>
       <c r="R27" t="n">
-        <v>6517327</v>
+        <v>6517447</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3646,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3034,7 +3034,7 @@
         <v>121174193</v>
       </c>
       <c r="B22" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>121517750</v>
       </c>
       <c r="B23" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121512078</v>
+        <v>121511809</v>
       </c>
       <c r="B24" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577307</v>
+        <v>577208</v>
       </c>
       <c r="R24" t="n">
-        <v>6517405</v>
+        <v>6517447</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516501</v>
+        <v>121512671</v>
       </c>
       <c r="B25" t="n">
-        <v>78252</v>
+        <v>90739</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3374,21 +3374,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3398,13 +3398,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577280</v>
+        <v>577745</v>
       </c>
       <c r="R25" t="n">
-        <v>6517445</v>
+        <v>6517128</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121512671</v>
+        <v>121512473</v>
       </c>
       <c r="B26" t="n">
-        <v>90733</v>
+        <v>79226</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,21 +3476,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577745</v>
+        <v>577437</v>
       </c>
       <c r="R26" t="n">
-        <v>6517128</v>
+        <v>6517104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121511679</v>
+        <v>121516501</v>
       </c>
       <c r="B27" t="n">
-        <v>79225</v>
+        <v>78253</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577208</v>
+        <v>577280</v>
       </c>
       <c r="R27" t="n">
-        <v>6517447</v>
+        <v>6517445</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121512473</v>
+        <v>121512078</v>
       </c>
       <c r="B28" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577437</v>
+        <v>577307</v>
       </c>
       <c r="R28" t="n">
-        <v>6517104</v>
+        <v>6517405</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121517750</v>
+        <v>121511809</v>
       </c>
       <c r="B23" t="n">
-        <v>80565</v>
+        <v>79227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,40 +3166,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577309</v>
+        <v>577208</v>
       </c>
       <c r="R23" t="n">
-        <v>6517327</v>
+        <v>6517447</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3237,7 +3234,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121511809</v>
+        <v>121512473</v>
       </c>
       <c r="B24" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,10 +3292,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577208</v>
+        <v>577437</v>
       </c>
       <c r="R24" t="n">
-        <v>6517447</v>
+        <v>6517104</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3358,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121512671</v>
+        <v>121517750</v>
       </c>
       <c r="B25" t="n">
-        <v>90739</v>
+        <v>80566</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3374,37 +3370,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577745</v>
+        <v>577309</v>
       </c>
       <c r="R25" t="n">
-        <v>6517128</v>
+        <v>6517327</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3442,6 +3441,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121512473</v>
+        <v>121516501</v>
       </c>
       <c r="B26" t="n">
-        <v>79226</v>
+        <v>78254</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,21 +3476,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3500,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577437</v>
+        <v>577280</v>
       </c>
       <c r="R26" t="n">
-        <v>6517104</v>
+        <v>6517445</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516501</v>
+        <v>121512671</v>
       </c>
       <c r="B27" t="n">
-        <v>78253</v>
+        <v>90740</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577280</v>
+        <v>577745</v>
       </c>
       <c r="R27" t="n">
-        <v>6517445</v>
+        <v>6517128</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>121512078</v>
       </c>
       <c r="B28" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,7 +3150,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121511809</v>
+        <v>121512473</v>
       </c>
       <c r="B23" t="n">
         <v>79227</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577208</v>
+        <v>577437</v>
       </c>
       <c r="R23" t="n">
-        <v>6517447</v>
+        <v>6517104</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121512473</v>
+        <v>121516501</v>
       </c>
       <c r="B24" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577437</v>
+        <v>577280</v>
       </c>
       <c r="R24" t="n">
-        <v>6517104</v>
+        <v>6517445</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121517750</v>
+        <v>121512671</v>
       </c>
       <c r="B25" t="n">
-        <v>80566</v>
+        <v>90740</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,40 +3370,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577309</v>
+        <v>577745</v>
       </c>
       <c r="R25" t="n">
-        <v>6517327</v>
+        <v>6517128</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3441,7 +3438,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3460,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516501</v>
+        <v>121517750</v>
       </c>
       <c r="B26" t="n">
-        <v>78254</v>
+        <v>80566</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,34 +3472,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577280</v>
+        <v>577309</v>
       </c>
       <c r="R26" t="n">
-        <v>6517445</v>
+        <v>6517327</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3544,6 +3543,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121512671</v>
+        <v>121511679</v>
       </c>
       <c r="B27" t="n">
-        <v>90740</v>
+        <v>79227</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577745</v>
+        <v>577208</v>
       </c>
       <c r="R27" t="n">
-        <v>6517128</v>
+        <v>6517447</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,7 +3150,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121512473</v>
+        <v>121511679</v>
       </c>
       <c r="B23" t="n">
         <v>79227</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577437</v>
+        <v>577208</v>
       </c>
       <c r="R23" t="n">
-        <v>6517104</v>
+        <v>6517447</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121516501</v>
+        <v>121512671</v>
       </c>
       <c r="B24" t="n">
-        <v>78254</v>
+        <v>90740</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,21 +3268,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577280</v>
+        <v>577745</v>
       </c>
       <c r="R24" t="n">
-        <v>6517445</v>
+        <v>6517128</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121512671</v>
+        <v>121517750</v>
       </c>
       <c r="B25" t="n">
-        <v>90740</v>
+        <v>80566</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,37 +3370,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577745</v>
+        <v>577309</v>
       </c>
       <c r="R25" t="n">
-        <v>6517128</v>
+        <v>6517327</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3438,6 +3441,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3456,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121517750</v>
+        <v>121512078</v>
       </c>
       <c r="B26" t="n">
-        <v>80566</v>
+        <v>79227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,37 +3476,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577309</v>
+        <v>577307</v>
       </c>
       <c r="R26" t="n">
-        <v>6517327</v>
+        <v>6517405</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3543,7 +3544,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121511679</v>
+        <v>121512473</v>
       </c>
       <c r="B27" t="n">
         <v>79227</v>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577208</v>
+        <v>577437</v>
       </c>
       <c r="R27" t="n">
-        <v>6517447</v>
+        <v>6517104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121512078</v>
+        <v>121516501</v>
       </c>
       <c r="B28" t="n">
-        <v>79227</v>
+        <v>78254</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577307</v>
+        <v>577280</v>
       </c>
       <c r="R28" t="n">
-        <v>6517405</v>
+        <v>6517445</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121511679</v>
+        <v>121517750</v>
       </c>
       <c r="B23" t="n">
-        <v>79227</v>
+        <v>80566</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,37 +3166,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577208</v>
+        <v>577309</v>
       </c>
       <c r="R23" t="n">
-        <v>6517447</v>
+        <v>6517327</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3234,6 +3237,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3252,10 +3256,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121512671</v>
+        <v>121516501</v>
       </c>
       <c r="B24" t="n">
-        <v>90740</v>
+        <v>78254</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3292,13 +3296,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577745</v>
+        <v>577280</v>
       </c>
       <c r="R24" t="n">
-        <v>6517128</v>
+        <v>6517445</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3354,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121517750</v>
+        <v>121511679</v>
       </c>
       <c r="B25" t="n">
-        <v>80566</v>
+        <v>79227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,40 +3374,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577309</v>
+        <v>577208</v>
       </c>
       <c r="R25" t="n">
-        <v>6517327</v>
+        <v>6517447</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3441,7 +3442,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516501</v>
+        <v>121512671</v>
       </c>
       <c r="B28" t="n">
-        <v>78254</v>
+        <v>90740</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577280</v>
+        <v>577745</v>
       </c>
       <c r="R28" t="n">
-        <v>6517445</v>
+        <v>6517128</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121517750</v>
+        <v>121511679</v>
       </c>
       <c r="B23" t="n">
-        <v>80566</v>
+        <v>79234</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,40 +3166,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577309</v>
+        <v>577208</v>
       </c>
       <c r="R23" t="n">
-        <v>6517327</v>
+        <v>6517447</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3237,7 +3234,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3259,7 +3255,7 @@
         <v>121516501</v>
       </c>
       <c r="B24" t="n">
-        <v>78254</v>
+        <v>78261</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3358,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121511679</v>
+        <v>121512078</v>
       </c>
       <c r="B25" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3398,13 +3394,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577208</v>
+        <v>577307</v>
       </c>
       <c r="R25" t="n">
-        <v>6517447</v>
+        <v>6517405</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,10 +3456,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121512078</v>
+        <v>121517750</v>
       </c>
       <c r="B26" t="n">
-        <v>79227</v>
+        <v>80573</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,34 +3472,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577307</v>
+        <v>577309</v>
       </c>
       <c r="R26" t="n">
-        <v>6517405</v>
+        <v>6517327</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3544,6 +3543,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>121512473</v>
       </c>
       <c r="B27" t="n">
-        <v>79227</v>
+        <v>79234</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>121512671</v>
       </c>
       <c r="B28" t="n">
-        <v>90740</v>
+        <v>90748</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,7 +3150,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121512078</v>
+        <v>121511679</v>
       </c>
       <c r="B23" t="n">
         <v>79234</v>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577307</v>
+        <v>577208</v>
       </c>
       <c r="R23" t="n">
-        <v>6517405</v>
+        <v>6517447</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121511679</v>
+        <v>121517750</v>
       </c>
       <c r="B25" t="n">
-        <v>79234</v>
+        <v>80573</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,37 +3370,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577208</v>
+        <v>577309</v>
       </c>
       <c r="R25" t="n">
-        <v>6517447</v>
+        <v>6517327</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3438,6 +3441,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3456,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121517750</v>
+        <v>121516501</v>
       </c>
       <c r="B26" t="n">
-        <v>80573</v>
+        <v>78261</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,37 +3476,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577309</v>
+        <v>577280</v>
       </c>
       <c r="R26" t="n">
-        <v>6517327</v>
+        <v>6517445</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3543,7 +3544,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516501</v>
+        <v>121512671</v>
       </c>
       <c r="B27" t="n">
-        <v>78261</v>
+        <v>90748</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577280</v>
+        <v>577745</v>
       </c>
       <c r="R27" t="n">
-        <v>6517445</v>
+        <v>6517128</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121512671</v>
+        <v>121512078</v>
       </c>
       <c r="B28" t="n">
-        <v>90748</v>
+        <v>79234</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577745</v>
+        <v>577307</v>
       </c>
       <c r="R28" t="n">
-        <v>6517128</v>
+        <v>6517405</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3460,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121516501</v>
+        <v>121512078</v>
       </c>
       <c r="B26" t="n">
-        <v>78261</v>
+        <v>79234</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,21 +3476,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577280</v>
+        <v>577307</v>
       </c>
       <c r="R26" t="n">
-        <v>6517445</v>
+        <v>6517405</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121512078</v>
+        <v>121516501</v>
       </c>
       <c r="B28" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577307</v>
+        <v>577280</v>
       </c>
       <c r="R28" t="n">
-        <v>6517405</v>
+        <v>6517445</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121511679</v>
+        <v>121517750</v>
       </c>
       <c r="B23" t="n">
-        <v>79234</v>
+        <v>80573</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,37 +3166,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577208</v>
+        <v>577309</v>
       </c>
       <c r="R23" t="n">
-        <v>6517447</v>
+        <v>6517327</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3234,6 +3237,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3252,7 +3256,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121512473</v>
+        <v>121512078</v>
       </c>
       <c r="B24" t="n">
         <v>79234</v>
@@ -3292,13 +3296,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577437</v>
+        <v>577307</v>
       </c>
       <c r="R24" t="n">
-        <v>6517104</v>
+        <v>6517405</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3354,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121517750</v>
+        <v>121512671</v>
       </c>
       <c r="B25" t="n">
-        <v>80573</v>
+        <v>90748</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,40 +3374,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577309</v>
+        <v>577745</v>
       </c>
       <c r="R25" t="n">
-        <v>6517327</v>
+        <v>6517128</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3441,7 +3442,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121512078</v>
+        <v>121511809</v>
       </c>
       <c r="B26" t="n">
         <v>79234</v>
@@ -3500,13 +3500,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577307</v>
+        <v>577208</v>
       </c>
       <c r="R26" t="n">
-        <v>6517405</v>
+        <v>6517447</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121512671</v>
+        <v>121516501</v>
       </c>
       <c r="B27" t="n">
-        <v>90748</v>
+        <v>78261</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577745</v>
+        <v>577280</v>
       </c>
       <c r="R27" t="n">
-        <v>6517128</v>
+        <v>6517445</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121516501</v>
+        <v>121512473</v>
       </c>
       <c r="B28" t="n">
-        <v>78261</v>
+        <v>79234</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577280</v>
+        <v>577437</v>
       </c>
       <c r="R28" t="n">
-        <v>6517445</v>
+        <v>6517104</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121517750</v>
+        <v>121511809</v>
       </c>
       <c r="B23" t="n">
-        <v>80573</v>
+        <v>79234</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,40 +3166,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577309</v>
+        <v>577208</v>
       </c>
       <c r="R23" t="n">
-        <v>6517327</v>
+        <v>6517447</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3237,7 +3234,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121512078</v>
+        <v>121517750</v>
       </c>
       <c r="B24" t="n">
-        <v>79234</v>
+        <v>80573</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3272,34 +3268,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skogsbyås, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577307</v>
+        <v>577309</v>
       </c>
       <c r="R24" t="n">
-        <v>6517405</v>
+        <v>6517327</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3340,6 +3339,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121512671</v>
+        <v>121516501</v>
       </c>
       <c r="B25" t="n">
-        <v>90748</v>
+        <v>78261</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3374,21 +3374,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3398,13 +3398,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577745</v>
+        <v>577280</v>
       </c>
       <c r="R25" t="n">
-        <v>6517128</v>
+        <v>6517445</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121511809</v>
+        <v>121512473</v>
       </c>
       <c r="B26" t="n">
         <v>79234</v>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577208</v>
+        <v>577437</v>
       </c>
       <c r="R26" t="n">
-        <v>6517447</v>
+        <v>6517104</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121516501</v>
+        <v>121512671</v>
       </c>
       <c r="B27" t="n">
-        <v>78261</v>
+        <v>90748</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,13 +3602,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577280</v>
+        <v>577745</v>
       </c>
       <c r="R27" t="n">
-        <v>6517445</v>
+        <v>6517128</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121512473</v>
+        <v>121512078</v>
       </c>
       <c r="B28" t="n">
         <v>79234</v>
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577437</v>
+        <v>577307</v>
       </c>
       <c r="R28" t="n">
-        <v>6517104</v>
+        <v>6517405</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 49039-2024 artfynd.xlsx
+++ b/artfynd/A 49039-2024 artfynd.xlsx
@@ -3150,7 +3150,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121511809</v>
+        <v>121512078</v>
       </c>
       <c r="B23" t="n">
         <v>79234</v>
@@ -3190,13 +3190,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577208</v>
+        <v>577307</v>
       </c>
       <c r="R23" t="n">
-        <v>6517447</v>
+        <v>6517405</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3358,10 +3358,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121516501</v>
+        <v>121511809</v>
       </c>
       <c r="B25" t="n">
-        <v>78261</v>
+        <v>79234</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3374,21 +3374,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3398,13 +3398,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577280</v>
+        <v>577208</v>
       </c>
       <c r="R25" t="n">
-        <v>6517445</v>
+        <v>6517447</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121512473</v>
+        <v>121512671</v>
       </c>
       <c r="B26" t="n">
-        <v>79234</v>
+        <v>90748</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3476,21 +3476,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577437</v>
+        <v>577745</v>
       </c>
       <c r="R26" t="n">
-        <v>6517104</v>
+        <v>6517128</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3562,10 +3562,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121512671</v>
+        <v>121512473</v>
       </c>
       <c r="B27" t="n">
-        <v>90748</v>
+        <v>79234</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,21 +3578,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3602,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577745</v>
+        <v>577437</v>
       </c>
       <c r="R27" t="n">
-        <v>6517128</v>
+        <v>6517104</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3664,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121512078</v>
+        <v>121516501</v>
       </c>
       <c r="B28" t="n">
-        <v>79234</v>
+        <v>78261</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3680,21 +3680,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3704,10 +3704,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577307</v>
+        <v>577280</v>
       </c>
       <c r="R28" t="n">
-        <v>6517405</v>
+        <v>6517445</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
